--- a/assingment/excel assingment/session -14/SESSION -14.xlsx
+++ b/assingment/excel assingment/session -14/SESSION -14.xlsx
@@ -1,25 +1,347 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Desktop\Tops\assingment\excel assingment\session -14\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A44BD6-F14C-4B4C-822C-F04BF927120F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="TASK - 1" sheetId="1" r:id="rId1"/>
+    <sheet name="TASK -2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="32" r:id="rId3"/>
+    <pivotCache cacheId="37" r:id="rId4"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="98">
+  <si>
+    <t>Order ID</t>
+  </si>
+  <si>
+    <t>Order Date</t>
+  </si>
+  <si>
+    <t>Restaurant</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Delivery Partner</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>ORD001</t>
+  </si>
+  <si>
+    <t>Domino's</t>
+  </si>
+  <si>
+    <t>Ahmedabad</t>
+  </si>
+  <si>
+    <t>Zomato</t>
+  </si>
+  <si>
+    <t>ORD002</t>
+  </si>
+  <si>
+    <t>McDonald's</t>
+  </si>
+  <si>
+    <t>Surat</t>
+  </si>
+  <si>
+    <t>Swiggy</t>
+  </si>
+  <si>
+    <t>ORD003</t>
+  </si>
+  <si>
+    <t>KFC</t>
+  </si>
+  <si>
+    <t>Vadodara</t>
+  </si>
+  <si>
+    <t>Blinkit</t>
+  </si>
+  <si>
+    <t>ORD004</t>
+  </si>
+  <si>
+    <t>Pizza Hut</t>
+  </si>
+  <si>
+    <t>Rajkot</t>
+  </si>
+  <si>
+    <t>ORD005</t>
+  </si>
+  <si>
+    <t>Subway</t>
+  </si>
+  <si>
+    <t>ORD006</t>
+  </si>
+  <si>
+    <t>Burger King</t>
+  </si>
+  <si>
+    <t>ORD007</t>
+  </si>
+  <si>
+    <t>La Pino'z Pizza</t>
+  </si>
+  <si>
+    <t>ORD008</t>
+  </si>
+  <si>
+    <t>Taco Bell</t>
+  </si>
+  <si>
+    <t>ORD009</t>
+  </si>
+  <si>
+    <t>Hocco Eatery</t>
+  </si>
+  <si>
+    <t>ORD010</t>
+  </si>
+  <si>
+    <t>Honest</t>
+  </si>
+  <si>
+    <t>ORD011</t>
+  </si>
+  <si>
+    <t>ORD012</t>
+  </si>
+  <si>
+    <t>ORD013</t>
+  </si>
+  <si>
+    <t>ORD014</t>
+  </si>
+  <si>
+    <t>ORD015</t>
+  </si>
+  <si>
+    <t>ORD016</t>
+  </si>
+  <si>
+    <t>ORD017</t>
+  </si>
+  <si>
+    <t>ORD018</t>
+  </si>
+  <si>
+    <t>ORD019</t>
+  </si>
+  <si>
+    <t>ORD020</t>
+  </si>
+  <si>
+    <t>ORD021</t>
+  </si>
+  <si>
+    <t>ORD022</t>
+  </si>
+  <si>
+    <t>ORD023</t>
+  </si>
+  <si>
+    <t>ORD024</t>
+  </si>
+  <si>
+    <t>ORD025</t>
+  </si>
+  <si>
+    <t>ORD026</t>
+  </si>
+  <si>
+    <t>ORD027</t>
+  </si>
+  <si>
+    <t>ORD028</t>
+  </si>
+  <si>
+    <t>ORD029</t>
+  </si>
+  <si>
+    <t>ORD030</t>
+  </si>
+  <si>
+    <t>ORD031</t>
+  </si>
+  <si>
+    <t>ORD032</t>
+  </si>
+  <si>
+    <t>ORD033</t>
+  </si>
+  <si>
+    <t>ORD034</t>
+  </si>
+  <si>
+    <t>ORD035</t>
+  </si>
+  <si>
+    <t>ORD036</t>
+  </si>
+  <si>
+    <t>ORD037</t>
+  </si>
+  <si>
+    <t>ORD038</t>
+  </si>
+  <si>
+    <t>ORD039</t>
+  </si>
+  <si>
+    <t>ORD040</t>
+  </si>
+  <si>
+    <t>ORD041</t>
+  </si>
+  <si>
+    <t>ORD042</t>
+  </si>
+  <si>
+    <t>ORD043</t>
+  </si>
+  <si>
+    <t>ORD044</t>
+  </si>
+  <si>
+    <t>ORD045</t>
+  </si>
+  <si>
+    <t>ORD046</t>
+  </si>
+  <si>
+    <t>ORD047</t>
+  </si>
+  <si>
+    <t>ORD048</t>
+  </si>
+  <si>
+    <t>ORD049</t>
+  </si>
+  <si>
+    <t>ORD050</t>
+  </si>
+  <si>
+    <t>ORD051</t>
+  </si>
+  <si>
+    <t>ORD052</t>
+  </si>
+  <si>
+    <t>ORD053</t>
+  </si>
+  <si>
+    <t>ORD054</t>
+  </si>
+  <si>
+    <t>ORD055</t>
+  </si>
+  <si>
+    <t>ORD056</t>
+  </si>
+  <si>
+    <t>ORD057</t>
+  </si>
+  <si>
+    <t>ORD058</t>
+  </si>
+  <si>
+    <t>ORD059</t>
+  </si>
+  <si>
+    <t>ORD060</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Amount</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>Jun</t>
+  </si>
+  <si>
+    <t>Jul</t>
+  </si>
+  <si>
+    <t>Aug</t>
+  </si>
+  <si>
+    <t>Sep</t>
+  </si>
+  <si>
+    <t>Oct</t>
+  </si>
+  <si>
+    <t>Nov</t>
+  </si>
+  <si>
+    <t>Dec</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -49,13 +371,67 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="14">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -66,6 +442,2626 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="HP" refreshedDate="46226.819258680553" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="60" xr:uid="{3B6C0672-A3C2-4BF3-A287-DC6AB21C4E93}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:F61" sheet="TASK - 1"/>
+  </cacheSource>
+  <cacheFields count="6">
+    <cacheField name="Order ID" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Order Date" numFmtId="14">
+      <sharedItems containsNonDate="0" containsDate="1" containsMixedTypes="1" minDate="2025-01-18T00:00:00" maxDate="2025-12-19T00:00:00" count="120">
+        <d v="2025-05-01T00:00:00"/>
+        <d v="2025-08-01T00:00:00"/>
+        <d v="2025-12-01T00:00:00"/>
+        <d v="2025-01-18T00:00:00"/>
+        <d v="2025-01-25T00:00:00"/>
+        <d v="2025-01-30T00:00:00"/>
+        <d v="2025-05-02T00:00:00"/>
+        <d v="2025-09-02T00:00:00"/>
+        <d v="2025-02-14T00:00:00"/>
+        <d v="2025-02-20T00:00:00"/>
+        <d v="2025-02-25T00:00:00"/>
+        <d v="2025-02-28T00:00:00"/>
+        <d v="2025-04-03T00:00:00"/>
+        <d v="2025-09-03T00:00:00"/>
+        <d v="2025-03-15T00:00:00"/>
+        <d v="2025-03-22T00:00:00"/>
+        <d v="2025-03-28T00:00:00"/>
+        <d v="2025-03-31T00:00:00"/>
+        <d v="2025-04-04T00:00:00"/>
+        <d v="2025-10-04T00:00:00"/>
+        <d v="2025-04-15T00:00:00"/>
+        <d v="2025-04-19T00:00:00"/>
+        <d v="2025-04-24T00:00:00"/>
+        <d v="2025-04-29T00:00:00"/>
+        <d v="2025-05-05T00:00:00"/>
+        <d v="2025-10-05T00:00:00"/>
+        <d v="2025-05-15T00:00:00"/>
+        <d v="2025-05-20T00:00:00"/>
+        <d v="2025-05-25T00:00:00"/>
+        <d v="2025-05-30T00:00:00"/>
+        <d v="2025-04-06T00:00:00"/>
+        <d v="2025-09-06T00:00:00"/>
+        <d v="2025-06-14T00:00:00"/>
+        <d v="2025-06-19T00:00:00"/>
+        <d v="2025-06-24T00:00:00"/>
+        <d v="2025-06-29T00:00:00"/>
+        <d v="2025-05-07T00:00:00"/>
+        <d v="2025-10-07T00:00:00"/>
+        <d v="2025-07-15T00:00:00"/>
+        <d v="2025-07-20T00:00:00"/>
+        <d v="2025-07-25T00:00:00"/>
+        <d v="2025-07-30T00:00:00"/>
+        <d v="2025-05-08T00:00:00"/>
+        <d v="2025-10-08T00:00:00"/>
+        <d v="2025-08-15T00:00:00"/>
+        <d v="2025-08-20T00:00:00"/>
+        <d v="2025-08-25T00:00:00"/>
+        <d v="2025-08-30T00:00:00"/>
+        <d v="2025-05-09T00:00:00"/>
+        <d v="2025-10-09T00:00:00"/>
+        <d v="2025-10-15T00:00:00"/>
+        <d v="2025-10-20T00:00:00"/>
+        <d v="2025-10-25T00:00:00"/>
+        <d v="2025-10-30T00:00:00"/>
+        <d v="2025-05-11T00:00:00"/>
+        <d v="2025-12-11T00:00:00"/>
+        <d v="2025-11-18T00:00:00"/>
+        <d v="2025-11-24T00:00:00"/>
+        <d v="2025-05-12T00:00:00"/>
+        <d v="2025-12-18T00:00:00"/>
+        <s v="05-01-2025" u="1"/>
+        <s v="08-01-2025" u="1"/>
+        <s v="12-01-2025" u="1"/>
+        <s v="18-01-2025" u="1"/>
+        <s v="25-01-2025" u="1"/>
+        <s v="30-01-2025" u="1"/>
+        <s v="05-02-2025" u="1"/>
+        <s v="09-02-2025" u="1"/>
+        <s v="14-02-2025" u="1"/>
+        <s v="20-02-2025" u="1"/>
+        <s v="25-02-2025" u="1"/>
+        <s v="28-02-2025" u="1"/>
+        <s v="04-03-2025" u="1"/>
+        <s v="09-03-2025" u="1"/>
+        <s v="15-03-2025" u="1"/>
+        <s v="22-03-2025" u="1"/>
+        <s v="28-03-2025" u="1"/>
+        <s v="31-03-2025" u="1"/>
+        <s v="04-04-2025" u="1"/>
+        <s v="10-04-2025" u="1"/>
+        <s v="15-04-2025" u="1"/>
+        <s v="19-04-2025" u="1"/>
+        <s v="24-04-2025" u="1"/>
+        <s v="29-04-2025" u="1"/>
+        <s v="05-05-2025" u="1"/>
+        <s v="10-05-2025" u="1"/>
+        <s v="15-05-2025" u="1"/>
+        <s v="20-05-2025" u="1"/>
+        <s v="25-05-2025" u="1"/>
+        <s v="30-05-2025" u="1"/>
+        <s v="04-06-2025" u="1"/>
+        <s v="09-06-2025" u="1"/>
+        <s v="14-06-2025" u="1"/>
+        <s v="19-06-2025" u="1"/>
+        <s v="24-06-2025" u="1"/>
+        <s v="29-06-2025" u="1"/>
+        <s v="05-07-2025" u="1"/>
+        <s v="10-07-2025" u="1"/>
+        <s v="15-07-2025" u="1"/>
+        <s v="20-07-2025" u="1"/>
+        <s v="25-07-2025" u="1"/>
+        <s v="30-07-2025" u="1"/>
+        <s v="05-08-2025" u="1"/>
+        <s v="10-08-2025" u="1"/>
+        <s v="15-08-2025" u="1"/>
+        <s v="20-08-2025" u="1"/>
+        <s v="25-08-2025" u="1"/>
+        <s v="30-08-2025" u="1"/>
+        <s v="05-09-2025" u="1"/>
+        <s v="10-09-2025" u="1"/>
+        <s v="15-10-2025" u="1"/>
+        <s v="20-10-2025" u="1"/>
+        <s v="25-10-2025" u="1"/>
+        <s v="30-10-2025" u="1"/>
+        <s v="05-11-2025" u="1"/>
+        <s v="12-11-2025" u="1"/>
+        <s v="18-11-2025" u="1"/>
+        <s v="24-11-2025" u="1"/>
+        <s v="05-12-2025" u="1"/>
+        <s v="18-12-2025" u="1"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Restaurant" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="City" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Delivery Partner" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Amount" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="270" maxValue="780"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="HP" refreshedDate="46226.830370370371" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="60" xr:uid="{F6D10708-3E08-4A2D-A8DB-1B4F7B927950}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:F61" sheet="TASK -2"/>
+  </cacheSource>
+  <cacheFields count="8">
+    <cacheField name="Order ID" numFmtId="0">
+      <sharedItems count="60">
+        <s v="ORD001"/>
+        <s v="ORD002"/>
+        <s v="ORD003"/>
+        <s v="ORD004"/>
+        <s v="ORD005"/>
+        <s v="ORD006"/>
+        <s v="ORD007"/>
+        <s v="ORD008"/>
+        <s v="ORD009"/>
+        <s v="ORD010"/>
+        <s v="ORD011"/>
+        <s v="ORD012"/>
+        <s v="ORD013"/>
+        <s v="ORD014"/>
+        <s v="ORD015"/>
+        <s v="ORD016"/>
+        <s v="ORD017"/>
+        <s v="ORD018"/>
+        <s v="ORD019"/>
+        <s v="ORD020"/>
+        <s v="ORD021"/>
+        <s v="ORD022"/>
+        <s v="ORD023"/>
+        <s v="ORD024"/>
+        <s v="ORD025"/>
+        <s v="ORD026"/>
+        <s v="ORD027"/>
+        <s v="ORD028"/>
+        <s v="ORD029"/>
+        <s v="ORD030"/>
+        <s v="ORD031"/>
+        <s v="ORD032"/>
+        <s v="ORD033"/>
+        <s v="ORD034"/>
+        <s v="ORD035"/>
+        <s v="ORD036"/>
+        <s v="ORD037"/>
+        <s v="ORD038"/>
+        <s v="ORD039"/>
+        <s v="ORD040"/>
+        <s v="ORD041"/>
+        <s v="ORD042"/>
+        <s v="ORD043"/>
+        <s v="ORD044"/>
+        <s v="ORD045"/>
+        <s v="ORD046"/>
+        <s v="ORD047"/>
+        <s v="ORD048"/>
+        <s v="ORD049"/>
+        <s v="ORD050"/>
+        <s v="ORD051"/>
+        <s v="ORD052"/>
+        <s v="ORD053"/>
+        <s v="ORD054"/>
+        <s v="ORD055"/>
+        <s v="ORD056"/>
+        <s v="ORD057"/>
+        <s v="ORD058"/>
+        <s v="ORD059"/>
+        <s v="ORD060"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Order Date" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2025-01-05T00:00:00" maxDate="2025-12-19T00:00:00" count="60">
+        <d v="2025-01-05T00:00:00"/>
+        <d v="2025-01-08T00:00:00"/>
+        <d v="2025-01-12T00:00:00"/>
+        <d v="2025-01-18T00:00:00"/>
+        <d v="2025-01-25T00:00:00"/>
+        <d v="2025-01-30T00:00:00"/>
+        <d v="2025-02-05T00:00:00"/>
+        <d v="2025-02-09T00:00:00"/>
+        <d v="2025-02-14T00:00:00"/>
+        <d v="2025-02-20T00:00:00"/>
+        <d v="2025-02-25T00:00:00"/>
+        <d v="2025-02-28T00:00:00"/>
+        <d v="2025-03-04T00:00:00"/>
+        <d v="2025-03-09T00:00:00"/>
+        <d v="2025-03-15T00:00:00"/>
+        <d v="2025-03-22T00:00:00"/>
+        <d v="2025-03-28T00:00:00"/>
+        <d v="2025-03-31T00:00:00"/>
+        <d v="2025-04-04T00:00:00"/>
+        <d v="2025-04-10T00:00:00"/>
+        <d v="2025-04-15T00:00:00"/>
+        <d v="2025-04-19T00:00:00"/>
+        <d v="2025-04-24T00:00:00"/>
+        <d v="2025-04-29T00:00:00"/>
+        <d v="2025-05-05T00:00:00"/>
+        <d v="2025-05-10T00:00:00"/>
+        <d v="2025-05-15T00:00:00"/>
+        <d v="2025-05-20T00:00:00"/>
+        <d v="2025-05-25T00:00:00"/>
+        <d v="2025-05-30T00:00:00"/>
+        <d v="2025-06-04T00:00:00"/>
+        <d v="2025-06-09T00:00:00"/>
+        <d v="2025-06-14T00:00:00"/>
+        <d v="2025-06-19T00:00:00"/>
+        <d v="2025-06-24T00:00:00"/>
+        <d v="2025-06-29T00:00:00"/>
+        <d v="2025-07-05T00:00:00"/>
+        <d v="2025-07-10T00:00:00"/>
+        <d v="2025-07-15T00:00:00"/>
+        <d v="2025-07-20T00:00:00"/>
+        <d v="2025-07-25T00:00:00"/>
+        <d v="2025-07-30T00:00:00"/>
+        <d v="2025-08-05T00:00:00"/>
+        <d v="2025-08-10T00:00:00"/>
+        <d v="2025-08-15T00:00:00"/>
+        <d v="2025-08-20T00:00:00"/>
+        <d v="2025-08-25T00:00:00"/>
+        <d v="2025-08-30T00:00:00"/>
+        <d v="2025-09-05T00:00:00"/>
+        <d v="2025-09-10T00:00:00"/>
+        <d v="2025-10-15T00:00:00"/>
+        <d v="2025-10-20T00:00:00"/>
+        <d v="2025-10-25T00:00:00"/>
+        <d v="2025-10-30T00:00:00"/>
+        <d v="2025-11-05T00:00:00"/>
+        <d v="2025-11-12T00:00:00"/>
+        <d v="2025-11-18T00:00:00"/>
+        <d v="2025-11-24T00:00:00"/>
+        <d v="2025-12-05T00:00:00"/>
+        <d v="2025-12-18T00:00:00"/>
+      </sharedItems>
+      <fieldGroup par="7"/>
+    </cacheField>
+    <cacheField name="Restaurant" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="City" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Delivery Partner" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Amount" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="270" maxValue="780"/>
+    </cacheField>
+    <cacheField name="Days (Order Date)" numFmtId="0" databaseField="0">
+      <fieldGroup base="1">
+        <rangePr groupBy="days" startDate="2025-01-05T00:00:00" endDate="2025-12-19T00:00:00"/>
+        <groupItems count="368">
+          <s v="&lt;05-01-2025"/>
+          <s v="01-Jan"/>
+          <s v="02-Jan"/>
+          <s v="03-Jan"/>
+          <s v="04-Jan"/>
+          <s v="05-Jan"/>
+          <s v="06-Jan"/>
+          <s v="07-Jan"/>
+          <s v="08-Jan"/>
+          <s v="09-Jan"/>
+          <s v="10-Jan"/>
+          <s v="11-Jan"/>
+          <s v="12-Jan"/>
+          <s v="13-Jan"/>
+          <s v="14-Jan"/>
+          <s v="15-Jan"/>
+          <s v="16-Jan"/>
+          <s v="17-Jan"/>
+          <s v="18-Jan"/>
+          <s v="19-Jan"/>
+          <s v="20-Jan"/>
+          <s v="21-Jan"/>
+          <s v="22-Jan"/>
+          <s v="23-Jan"/>
+          <s v="24-Jan"/>
+          <s v="25-Jan"/>
+          <s v="26-Jan"/>
+          <s v="27-Jan"/>
+          <s v="28-Jan"/>
+          <s v="29-Jan"/>
+          <s v="30-Jan"/>
+          <s v="31-Jan"/>
+          <s v="01-Feb"/>
+          <s v="02-Feb"/>
+          <s v="03-Feb"/>
+          <s v="04-Feb"/>
+          <s v="05-Feb"/>
+          <s v="06-Feb"/>
+          <s v="07-Feb"/>
+          <s v="08-Feb"/>
+          <s v="09-Feb"/>
+          <s v="10-Feb"/>
+          <s v="11-Feb"/>
+          <s v="12-Feb"/>
+          <s v="13-Feb"/>
+          <s v="14-Feb"/>
+          <s v="15-Feb"/>
+          <s v="16-Feb"/>
+          <s v="17-Feb"/>
+          <s v="18-Feb"/>
+          <s v="19-Feb"/>
+          <s v="20-Feb"/>
+          <s v="21-Feb"/>
+          <s v="22-Feb"/>
+          <s v="23-Feb"/>
+          <s v="24-Feb"/>
+          <s v="25-Feb"/>
+          <s v="26-Feb"/>
+          <s v="27-Feb"/>
+          <s v="28-Feb"/>
+          <s v="29-Feb"/>
+          <s v="01-Mar"/>
+          <s v="02-Mar"/>
+          <s v="03-Mar"/>
+          <s v="04-Mar"/>
+          <s v="05-Mar"/>
+          <s v="06-Mar"/>
+          <s v="07-Mar"/>
+          <s v="08-Mar"/>
+          <s v="09-Mar"/>
+          <s v="10-Mar"/>
+          <s v="11-Mar"/>
+          <s v="12-Mar"/>
+          <s v="13-Mar"/>
+          <s v="14-Mar"/>
+          <s v="15-Mar"/>
+          <s v="16-Mar"/>
+          <s v="17-Mar"/>
+          <s v="18-Mar"/>
+          <s v="19-Mar"/>
+          <s v="20-Mar"/>
+          <s v="21-Mar"/>
+          <s v="22-Mar"/>
+          <s v="23-Mar"/>
+          <s v="24-Mar"/>
+          <s v="25-Mar"/>
+          <s v="26-Mar"/>
+          <s v="27-Mar"/>
+          <s v="28-Mar"/>
+          <s v="29-Mar"/>
+          <s v="30-Mar"/>
+          <s v="31-Mar"/>
+          <s v="01-Apr"/>
+          <s v="02-Apr"/>
+          <s v="03-Apr"/>
+          <s v="04-Apr"/>
+          <s v="05-Apr"/>
+          <s v="06-Apr"/>
+          <s v="07-Apr"/>
+          <s v="08-Apr"/>
+          <s v="09-Apr"/>
+          <s v="10-Apr"/>
+          <s v="11-Apr"/>
+          <s v="12-Apr"/>
+          <s v="13-Apr"/>
+          <s v="14-Apr"/>
+          <s v="15-Apr"/>
+          <s v="16-Apr"/>
+          <s v="17-Apr"/>
+          <s v="18-Apr"/>
+          <s v="19-Apr"/>
+          <s v="20-Apr"/>
+          <s v="21-Apr"/>
+          <s v="22-Apr"/>
+          <s v="23-Apr"/>
+          <s v="24-Apr"/>
+          <s v="25-Apr"/>
+          <s v="26-Apr"/>
+          <s v="27-Apr"/>
+          <s v="28-Apr"/>
+          <s v="29-Apr"/>
+          <s v="30-Apr"/>
+          <s v="01-May"/>
+          <s v="02-May"/>
+          <s v="03-May"/>
+          <s v="04-May"/>
+          <s v="05-May"/>
+          <s v="06-May"/>
+          <s v="07-May"/>
+          <s v="08-May"/>
+          <s v="09-May"/>
+          <s v="10-May"/>
+          <s v="11-May"/>
+          <s v="12-May"/>
+          <s v="13-May"/>
+          <s v="14-May"/>
+          <s v="15-May"/>
+          <s v="16-May"/>
+          <s v="17-May"/>
+          <s v="18-May"/>
+          <s v="19-May"/>
+          <s v="20-May"/>
+          <s v="21-May"/>
+          <s v="22-May"/>
+          <s v="23-May"/>
+          <s v="24-May"/>
+          <s v="25-May"/>
+          <s v="26-May"/>
+          <s v="27-May"/>
+          <s v="28-May"/>
+          <s v="29-May"/>
+          <s v="30-May"/>
+          <s v="31-May"/>
+          <s v="01-Jun"/>
+          <s v="02-Jun"/>
+          <s v="03-Jun"/>
+          <s v="04-Jun"/>
+          <s v="05-Jun"/>
+          <s v="06-Jun"/>
+          <s v="07-Jun"/>
+          <s v="08-Jun"/>
+          <s v="09-Jun"/>
+          <s v="10-Jun"/>
+          <s v="11-Jun"/>
+          <s v="12-Jun"/>
+          <s v="13-Jun"/>
+          <s v="14-Jun"/>
+          <s v="15-Jun"/>
+          <s v="16-Jun"/>
+          <s v="17-Jun"/>
+          <s v="18-Jun"/>
+          <s v="19-Jun"/>
+          <s v="20-Jun"/>
+          <s v="21-Jun"/>
+          <s v="22-Jun"/>
+          <s v="23-Jun"/>
+          <s v="24-Jun"/>
+          <s v="25-Jun"/>
+          <s v="26-Jun"/>
+          <s v="27-Jun"/>
+          <s v="28-Jun"/>
+          <s v="29-Jun"/>
+          <s v="30-Jun"/>
+          <s v="01-Jul"/>
+          <s v="02-Jul"/>
+          <s v="03-Jul"/>
+          <s v="04-Jul"/>
+          <s v="05-Jul"/>
+          <s v="06-Jul"/>
+          <s v="07-Jul"/>
+          <s v="08-Jul"/>
+          <s v="09-Jul"/>
+          <s v="10-Jul"/>
+          <s v="11-Jul"/>
+          <s v="12-Jul"/>
+          <s v="13-Jul"/>
+          <s v="14-Jul"/>
+          <s v="15-Jul"/>
+          <s v="16-Jul"/>
+          <s v="17-Jul"/>
+          <s v="18-Jul"/>
+          <s v="19-Jul"/>
+          <s v="20-Jul"/>
+          <s v="21-Jul"/>
+          <s v="22-Jul"/>
+          <s v="23-Jul"/>
+          <s v="24-Jul"/>
+          <s v="25-Jul"/>
+          <s v="26-Jul"/>
+          <s v="27-Jul"/>
+          <s v="28-Jul"/>
+          <s v="29-Jul"/>
+          <s v="30-Jul"/>
+          <s v="31-Jul"/>
+          <s v="01-Aug"/>
+          <s v="02-Aug"/>
+          <s v="03-Aug"/>
+          <s v="04-Aug"/>
+          <s v="05-Aug"/>
+          <s v="06-Aug"/>
+          <s v="07-Aug"/>
+          <s v="08-Aug"/>
+          <s v="09-Aug"/>
+          <s v="10-Aug"/>
+          <s v="11-Aug"/>
+          <s v="12-Aug"/>
+          <s v="13-Aug"/>
+          <s v="14-Aug"/>
+          <s v="15-Aug"/>
+          <s v="16-Aug"/>
+          <s v="17-Aug"/>
+          <s v="18-Aug"/>
+          <s v="19-Aug"/>
+          <s v="20-Aug"/>
+          <s v="21-Aug"/>
+          <s v="22-Aug"/>
+          <s v="23-Aug"/>
+          <s v="24-Aug"/>
+          <s v="25-Aug"/>
+          <s v="26-Aug"/>
+          <s v="27-Aug"/>
+          <s v="28-Aug"/>
+          <s v="29-Aug"/>
+          <s v="30-Aug"/>
+          <s v="31-Aug"/>
+          <s v="01-Sep"/>
+          <s v="02-Sep"/>
+          <s v="03-Sep"/>
+          <s v="04-Sep"/>
+          <s v="05-Sep"/>
+          <s v="06-Sep"/>
+          <s v="07-Sep"/>
+          <s v="08-Sep"/>
+          <s v="09-Sep"/>
+          <s v="10-Sep"/>
+          <s v="11-Sep"/>
+          <s v="12-Sep"/>
+          <s v="13-Sep"/>
+          <s v="14-Sep"/>
+          <s v="15-Sep"/>
+          <s v="16-Sep"/>
+          <s v="17-Sep"/>
+          <s v="18-Sep"/>
+          <s v="19-Sep"/>
+          <s v="20-Sep"/>
+          <s v="21-Sep"/>
+          <s v="22-Sep"/>
+          <s v="23-Sep"/>
+          <s v="24-Sep"/>
+          <s v="25-Sep"/>
+          <s v="26-Sep"/>
+          <s v="27-Sep"/>
+          <s v="28-Sep"/>
+          <s v="29-Sep"/>
+          <s v="30-Sep"/>
+          <s v="01-Oct"/>
+          <s v="02-Oct"/>
+          <s v="03-Oct"/>
+          <s v="04-Oct"/>
+          <s v="05-Oct"/>
+          <s v="06-Oct"/>
+          <s v="07-Oct"/>
+          <s v="08-Oct"/>
+          <s v="09-Oct"/>
+          <s v="10-Oct"/>
+          <s v="11-Oct"/>
+          <s v="12-Oct"/>
+          <s v="13-Oct"/>
+          <s v="14-Oct"/>
+          <s v="15-Oct"/>
+          <s v="16-Oct"/>
+          <s v="17-Oct"/>
+          <s v="18-Oct"/>
+          <s v="19-Oct"/>
+          <s v="20-Oct"/>
+          <s v="21-Oct"/>
+          <s v="22-Oct"/>
+          <s v="23-Oct"/>
+          <s v="24-Oct"/>
+          <s v="25-Oct"/>
+          <s v="26-Oct"/>
+          <s v="27-Oct"/>
+          <s v="28-Oct"/>
+          <s v="29-Oct"/>
+          <s v="30-Oct"/>
+          <s v="31-Oct"/>
+          <s v="01-Nov"/>
+          <s v="02-Nov"/>
+          <s v="03-Nov"/>
+          <s v="04-Nov"/>
+          <s v="05-Nov"/>
+          <s v="06-Nov"/>
+          <s v="07-Nov"/>
+          <s v="08-Nov"/>
+          <s v="09-Nov"/>
+          <s v="10-Nov"/>
+          <s v="11-Nov"/>
+          <s v="12-Nov"/>
+          <s v="13-Nov"/>
+          <s v="14-Nov"/>
+          <s v="15-Nov"/>
+          <s v="16-Nov"/>
+          <s v="17-Nov"/>
+          <s v="18-Nov"/>
+          <s v="19-Nov"/>
+          <s v="20-Nov"/>
+          <s v="21-Nov"/>
+          <s v="22-Nov"/>
+          <s v="23-Nov"/>
+          <s v="24-Nov"/>
+          <s v="25-Nov"/>
+          <s v="26-Nov"/>
+          <s v="27-Nov"/>
+          <s v="28-Nov"/>
+          <s v="29-Nov"/>
+          <s v="30-Nov"/>
+          <s v="01-Dec"/>
+          <s v="02-Dec"/>
+          <s v="03-Dec"/>
+          <s v="04-Dec"/>
+          <s v="05-Dec"/>
+          <s v="06-Dec"/>
+          <s v="07-Dec"/>
+          <s v="08-Dec"/>
+          <s v="09-Dec"/>
+          <s v="10-Dec"/>
+          <s v="11-Dec"/>
+          <s v="12-Dec"/>
+          <s v="13-Dec"/>
+          <s v="14-Dec"/>
+          <s v="15-Dec"/>
+          <s v="16-Dec"/>
+          <s v="17-Dec"/>
+          <s v="18-Dec"/>
+          <s v="19-Dec"/>
+          <s v="20-Dec"/>
+          <s v="21-Dec"/>
+          <s v="22-Dec"/>
+          <s v="23-Dec"/>
+          <s v="24-Dec"/>
+          <s v="25-Dec"/>
+          <s v="26-Dec"/>
+          <s v="27-Dec"/>
+          <s v="28-Dec"/>
+          <s v="29-Dec"/>
+          <s v="30-Dec"/>
+          <s v="31-Dec"/>
+          <s v="&gt;19-12-2025"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Months (Order Date)" numFmtId="0" databaseField="0">
+      <fieldGroup base="1">
+        <rangePr groupBy="months" startDate="2025-01-05T00:00:00" endDate="2025-12-19T00:00:00"/>
+        <groupItems count="14">
+          <s v="&lt;05-01-2025"/>
+          <s v="Jan"/>
+          <s v="Feb"/>
+          <s v="Mar"/>
+          <s v="Apr"/>
+          <s v="May"/>
+          <s v="Jun"/>
+          <s v="Jul"/>
+          <s v="Aug"/>
+          <s v="Sep"/>
+          <s v="Oct"/>
+          <s v="Nov"/>
+          <s v="Dec"/>
+          <s v="&gt;19-12-2025"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="60">
+  <r>
+    <s v="ORD001"/>
+    <x v="0"/>
+    <s v="Domino's"/>
+    <s v="Ahmedabad"/>
+    <s v="Zomato"/>
+    <n v="450"/>
+  </r>
+  <r>
+    <s v="ORD002"/>
+    <x v="1"/>
+    <s v="McDonald's"/>
+    <s v="Surat"/>
+    <s v="Swiggy"/>
+    <n v="320"/>
+  </r>
+  <r>
+    <s v="ORD003"/>
+    <x v="2"/>
+    <s v="KFC"/>
+    <s v="Vadodara"/>
+    <s v="Blinkit"/>
+    <n v="550"/>
+  </r>
+  <r>
+    <s v="ORD004"/>
+    <x v="3"/>
+    <s v="Pizza Hut"/>
+    <s v="Rajkot"/>
+    <s v="Zomato"/>
+    <n v="700"/>
+  </r>
+  <r>
+    <s v="ORD005"/>
+    <x v="4"/>
+    <s v="Subway"/>
+    <s v="Ahmedabad"/>
+    <s v="Swiggy"/>
+    <n v="280"/>
+  </r>
+  <r>
+    <s v="ORD006"/>
+    <x v="5"/>
+    <s v="Burger King"/>
+    <s v="Surat"/>
+    <s v="Zomato"/>
+    <n v="390"/>
+  </r>
+  <r>
+    <s v="ORD007"/>
+    <x v="6"/>
+    <s v="La Pino'z Pizza"/>
+    <s v="Ahmedabad"/>
+    <s v="Blinkit"/>
+    <n v="620"/>
+  </r>
+  <r>
+    <s v="ORD008"/>
+    <x v="7"/>
+    <s v="Taco Bell"/>
+    <s v="Vadodara"/>
+    <s v="Swiggy"/>
+    <n v="480"/>
+  </r>
+  <r>
+    <s v="ORD009"/>
+    <x v="8"/>
+    <s v="Hocco Eatery"/>
+    <s v="Rajkot"/>
+    <s v="Zomato"/>
+    <n v="540"/>
+  </r>
+  <r>
+    <s v="ORD010"/>
+    <x v="9"/>
+    <s v="Honest"/>
+    <s v="Ahmedabad"/>
+    <s v="Blinkit"/>
+    <n v="360"/>
+  </r>
+  <r>
+    <s v="ORD011"/>
+    <x v="10"/>
+    <s v="Domino's"/>
+    <s v="Surat"/>
+    <s v="Swiggy"/>
+    <n v="430"/>
+  </r>
+  <r>
+    <s v="ORD012"/>
+    <x v="11"/>
+    <s v="McDonald's"/>
+    <s v="Vadodara"/>
+    <s v="Zomato"/>
+    <n v="510"/>
+  </r>
+  <r>
+    <s v="ORD013"/>
+    <x v="12"/>
+    <s v="KFC"/>
+    <s v="Ahmedabad"/>
+    <s v="Blinkit"/>
+    <n v="610"/>
+  </r>
+  <r>
+    <s v="ORD014"/>
+    <x v="13"/>
+    <s v="Pizza Hut"/>
+    <s v="Rajkot"/>
+    <s v="Swiggy"/>
+    <n v="750"/>
+  </r>
+  <r>
+    <s v="ORD015"/>
+    <x v="14"/>
+    <s v="Subway"/>
+    <s v="Surat"/>
+    <s v="Zomato"/>
+    <n v="290"/>
+  </r>
+  <r>
+    <s v="ORD016"/>
+    <x v="15"/>
+    <s v="Burger King"/>
+    <s v="Vadodara"/>
+    <s v="Blinkit"/>
+    <n v="420"/>
+  </r>
+  <r>
+    <s v="ORD017"/>
+    <x v="16"/>
+    <s v="La Pino'z Pizza"/>
+    <s v="Ahmedabad"/>
+    <s v="Swiggy"/>
+    <n v="680"/>
+  </r>
+  <r>
+    <s v="ORD018"/>
+    <x v="17"/>
+    <s v="Taco Bell"/>
+    <s v="Rajkot"/>
+    <s v="Zomato"/>
+    <n v="460"/>
+  </r>
+  <r>
+    <s v="ORD019"/>
+    <x v="18"/>
+    <s v="Hocco Eatery"/>
+    <s v="Surat"/>
+    <s v="Blinkit"/>
+    <n v="530"/>
+  </r>
+  <r>
+    <s v="ORD020"/>
+    <x v="19"/>
+    <s v="Honest"/>
+    <s v="Vadodara"/>
+    <s v="Swiggy"/>
+    <n v="340"/>
+  </r>
+  <r>
+    <s v="ORD021"/>
+    <x v="20"/>
+    <s v="Domino's"/>
+    <s v="Ahmedabad"/>
+    <s v="Zomato"/>
+    <n v="440"/>
+  </r>
+  <r>
+    <s v="ORD022"/>
+    <x v="21"/>
+    <s v="McDonald's"/>
+    <s v="Rajkot"/>
+    <s v="Blinkit"/>
+    <n v="330"/>
+  </r>
+  <r>
+    <s v="ORD023"/>
+    <x v="22"/>
+    <s v="KFC"/>
+    <s v="Surat"/>
+    <s v="Swiggy"/>
+    <n v="590"/>
+  </r>
+  <r>
+    <s v="ORD024"/>
+    <x v="23"/>
+    <s v="Pizza Hut"/>
+    <s v="Vadodara"/>
+    <s v="Zomato"/>
+    <n v="720"/>
+  </r>
+  <r>
+    <s v="ORD025"/>
+    <x v="24"/>
+    <s v="Subway"/>
+    <s v="Ahmedabad"/>
+    <s v="Blinkit"/>
+    <n v="270"/>
+  </r>
+  <r>
+    <s v="ORD026"/>
+    <x v="25"/>
+    <s v="Burger King"/>
+    <s v="Surat"/>
+    <s v="Swiggy"/>
+    <n v="410"/>
+  </r>
+  <r>
+    <s v="ORD027"/>
+    <x v="26"/>
+    <s v="La Pino'z Pizza"/>
+    <s v="Rajkot"/>
+    <s v="Zomato"/>
+    <n v="650"/>
+  </r>
+  <r>
+    <s v="ORD028"/>
+    <x v="27"/>
+    <s v="Taco Bell"/>
+    <s v="Vadodara"/>
+    <s v="Blinkit"/>
+    <n v="470"/>
+  </r>
+  <r>
+    <s v="ORD029"/>
+    <x v="28"/>
+    <s v="Hocco Eatery"/>
+    <s v="Ahmedabad"/>
+    <s v="Swiggy"/>
+    <n v="520"/>
+  </r>
+  <r>
+    <s v="ORD030"/>
+    <x v="29"/>
+    <s v="Honest"/>
+    <s v="Surat"/>
+    <s v="Zomato"/>
+    <n v="350"/>
+  </r>
+  <r>
+    <s v="ORD031"/>
+    <x v="30"/>
+    <s v="Domino's"/>
+    <s v="Vadodara"/>
+    <s v="Blinkit"/>
+    <n v="460"/>
+  </r>
+  <r>
+    <s v="ORD032"/>
+    <x v="31"/>
+    <s v="McDonald's"/>
+    <s v="Ahmedabad"/>
+    <s v="Swiggy"/>
+    <n v="340"/>
+  </r>
+  <r>
+    <s v="ORD033"/>
+    <x v="32"/>
+    <s v="KFC"/>
+    <s v="Rajkot"/>
+    <s v="Zomato"/>
+    <n v="620"/>
+  </r>
+  <r>
+    <s v="ORD034"/>
+    <x v="33"/>
+    <s v="Pizza Hut"/>
+    <s v="Surat"/>
+    <s v="Blinkit"/>
+    <n v="780"/>
+  </r>
+  <r>
+    <s v="ORD035"/>
+    <x v="34"/>
+    <s v="Subway"/>
+    <s v="Vadodara"/>
+    <s v="Swiggy"/>
+    <n v="300"/>
+  </r>
+  <r>
+    <s v="ORD036"/>
+    <x v="35"/>
+    <s v="Burger King"/>
+    <s v="Ahmedabad"/>
+    <s v="Zomato"/>
+    <n v="430"/>
+  </r>
+  <r>
+    <s v="ORD037"/>
+    <x v="36"/>
+    <s v="La Pino'z Pizza"/>
+    <s v="Surat"/>
+    <s v="Blinkit"/>
+    <n v="690"/>
+  </r>
+  <r>
+    <s v="ORD038"/>
+    <x v="37"/>
+    <s v="Taco Bell"/>
+    <s v="Rajkot"/>
+    <s v="Swiggy"/>
+    <n v="490"/>
+  </r>
+  <r>
+    <s v="ORD039"/>
+    <x v="38"/>
+    <s v="Hocco Eatery"/>
+    <s v="Vadodara"/>
+    <s v="Zomato"/>
+    <n v="550"/>
+  </r>
+  <r>
+    <s v="ORD040"/>
+    <x v="39"/>
+    <s v="Honest"/>
+    <s v="Ahmedabad"/>
+    <s v="Blinkit"/>
+    <n v="370"/>
+  </r>
+  <r>
+    <s v="ORD041"/>
+    <x v="40"/>
+    <s v="Domino's"/>
+    <s v="Surat"/>
+    <s v="Swiggy"/>
+    <n v="450"/>
+  </r>
+  <r>
+    <s v="ORD042"/>
+    <x v="41"/>
+    <s v="McDonald's"/>
+    <s v="Rajkot"/>
+    <s v="Zomato"/>
+    <n v="340"/>
+  </r>
+  <r>
+    <s v="ORD043"/>
+    <x v="42"/>
+    <s v="KFC"/>
+    <s v="Vadodara"/>
+    <s v="Blinkit"/>
+    <n v="600"/>
+  </r>
+  <r>
+    <s v="ORD044"/>
+    <x v="43"/>
+    <s v="Pizza Hut"/>
+    <s v="Ahmedabad"/>
+    <s v="Swiggy"/>
+    <n v="740"/>
+  </r>
+  <r>
+    <s v="ORD045"/>
+    <x v="44"/>
+    <s v="Subway"/>
+    <s v="Surat"/>
+    <s v="Zomato"/>
+    <n v="310"/>
+  </r>
+  <r>
+    <s v="ORD046"/>
+    <x v="45"/>
+    <s v="Burger King"/>
+    <s v="Rajkot"/>
+    <s v="Blinkit"/>
+    <n v="440"/>
+  </r>
+  <r>
+    <s v="ORD047"/>
+    <x v="46"/>
+    <s v="La Pino'z Pizza"/>
+    <s v="Vadodara"/>
+    <s v="Swiggy"/>
+    <n v="670"/>
+  </r>
+  <r>
+    <s v="ORD048"/>
+    <x v="47"/>
+    <s v="Taco Bell"/>
+    <s v="Ahmedabad"/>
+    <s v="Zomato"/>
+    <n v="480"/>
+  </r>
+  <r>
+    <s v="ORD049"/>
+    <x v="48"/>
+    <s v="Hocco Eatery"/>
+    <s v="Surat"/>
+    <s v="Blinkit"/>
+    <n v="560"/>
+  </r>
+  <r>
+    <s v="ORD050"/>
+    <x v="49"/>
+    <s v="Honest"/>
+    <s v="Rajkot"/>
+    <s v="Swiggy"/>
+    <n v="360"/>
+  </r>
+  <r>
+    <s v="ORD051"/>
+    <x v="50"/>
+    <s v="Domino's"/>
+    <s v="Ahmedabad"/>
+    <s v="Zomato"/>
+    <n v="470"/>
+  </r>
+  <r>
+    <s v="ORD052"/>
+    <x v="51"/>
+    <s v="McDonald's"/>
+    <s v="Vadodara"/>
+    <s v="Blinkit"/>
+    <n v="350"/>
+  </r>
+  <r>
+    <s v="ORD053"/>
+    <x v="52"/>
+    <s v="KFC"/>
+    <s v="Surat"/>
+    <s v="Swiggy"/>
+    <n v="630"/>
+  </r>
+  <r>
+    <s v="ORD054"/>
+    <x v="53"/>
+    <s v="Pizza Hut"/>
+    <s v="Rajkot"/>
+    <s v="Zomato"/>
+    <n v="760"/>
+  </r>
+  <r>
+    <s v="ORD055"/>
+    <x v="54"/>
+    <s v="Subway"/>
+    <s v="Ahmedabad"/>
+    <s v="Blinkit"/>
+    <n v="320"/>
+  </r>
+  <r>
+    <s v="ORD056"/>
+    <x v="55"/>
+    <s v="Burger King"/>
+    <s v="Vadodara"/>
+    <s v="Swiggy"/>
+    <n v="450"/>
+  </r>
+  <r>
+    <s v="ORD057"/>
+    <x v="56"/>
+    <s v="La Pino'z Pizza"/>
+    <s v="Surat"/>
+    <s v="Zomato"/>
+    <n v="710"/>
+  </r>
+  <r>
+    <s v="ORD058"/>
+    <x v="57"/>
+    <s v="Taco Bell"/>
+    <s v="Rajkot"/>
+    <s v="Blinkit"/>
+    <n v="500"/>
+  </r>
+  <r>
+    <s v="ORD059"/>
+    <x v="58"/>
+    <s v="Hocco Eatery"/>
+    <s v="Ahmedabad"/>
+    <s v="Swiggy"/>
+    <n v="580"/>
+  </r>
+  <r>
+    <s v="ORD060"/>
+    <x v="59"/>
+    <s v="Honest"/>
+    <s v="Vadodara"/>
+    <s v="Zomato"/>
+    <n v="390"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="60">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Domino's"/>
+    <s v="Ahmedabad"/>
+    <s v="Zomato"/>
+    <n v="450"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="McDonald's"/>
+    <s v="Surat"/>
+    <s v="Swiggy"/>
+    <n v="320"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="KFC"/>
+    <s v="Vadodara"/>
+    <s v="Blinkit"/>
+    <n v="550"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <s v="Pizza Hut"/>
+    <s v="Rajkot"/>
+    <s v="Zomato"/>
+    <n v="700"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Subway"/>
+    <s v="Ahmedabad"/>
+    <s v="Swiggy"/>
+    <n v="280"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="5"/>
+    <s v="Burger King"/>
+    <s v="Surat"/>
+    <s v="Zomato"/>
+    <n v="390"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="6"/>
+    <s v="La Pino'z Pizza"/>
+    <s v="Ahmedabad"/>
+    <s v="Blinkit"/>
+    <n v="620"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="7"/>
+    <s v="Taco Bell"/>
+    <s v="Vadodara"/>
+    <s v="Swiggy"/>
+    <n v="480"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="8"/>
+    <s v="Hocco Eatery"/>
+    <s v="Rajkot"/>
+    <s v="Zomato"/>
+    <n v="540"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Honest"/>
+    <s v="Ahmedabad"/>
+    <s v="Blinkit"/>
+    <n v="360"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="10"/>
+    <s v="Domino's"/>
+    <s v="Surat"/>
+    <s v="Swiggy"/>
+    <n v="430"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="McDonald's"/>
+    <s v="Vadodara"/>
+    <s v="Zomato"/>
+    <n v="510"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="12"/>
+    <s v="KFC"/>
+    <s v="Ahmedabad"/>
+    <s v="Blinkit"/>
+    <n v="610"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="13"/>
+    <s v="Pizza Hut"/>
+    <s v="Rajkot"/>
+    <s v="Swiggy"/>
+    <n v="750"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="14"/>
+    <s v="Subway"/>
+    <s v="Surat"/>
+    <s v="Zomato"/>
+    <n v="290"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="15"/>
+    <s v="Burger King"/>
+    <s v="Vadodara"/>
+    <s v="Blinkit"/>
+    <n v="420"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <x v="16"/>
+    <s v="La Pino'z Pizza"/>
+    <s v="Ahmedabad"/>
+    <s v="Swiggy"/>
+    <n v="680"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <x v="17"/>
+    <s v="Taco Bell"/>
+    <s v="Rajkot"/>
+    <s v="Zomato"/>
+    <n v="460"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <x v="18"/>
+    <s v="Hocco Eatery"/>
+    <s v="Surat"/>
+    <s v="Blinkit"/>
+    <n v="530"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <x v="19"/>
+    <s v="Honest"/>
+    <s v="Vadodara"/>
+    <s v="Swiggy"/>
+    <n v="340"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <x v="20"/>
+    <s v="Domino's"/>
+    <s v="Ahmedabad"/>
+    <s v="Zomato"/>
+    <n v="440"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <x v="21"/>
+    <s v="McDonald's"/>
+    <s v="Rajkot"/>
+    <s v="Blinkit"/>
+    <n v="330"/>
+  </r>
+  <r>
+    <x v="22"/>
+    <x v="22"/>
+    <s v="KFC"/>
+    <s v="Surat"/>
+    <s v="Swiggy"/>
+    <n v="590"/>
+  </r>
+  <r>
+    <x v="23"/>
+    <x v="23"/>
+    <s v="Pizza Hut"/>
+    <s v="Vadodara"/>
+    <s v="Zomato"/>
+    <n v="720"/>
+  </r>
+  <r>
+    <x v="24"/>
+    <x v="24"/>
+    <s v="Subway"/>
+    <s v="Ahmedabad"/>
+    <s v="Blinkit"/>
+    <n v="270"/>
+  </r>
+  <r>
+    <x v="25"/>
+    <x v="25"/>
+    <s v="Burger King"/>
+    <s v="Surat"/>
+    <s v="Swiggy"/>
+    <n v="410"/>
+  </r>
+  <r>
+    <x v="26"/>
+    <x v="26"/>
+    <s v="La Pino'z Pizza"/>
+    <s v="Rajkot"/>
+    <s v="Zomato"/>
+    <n v="650"/>
+  </r>
+  <r>
+    <x v="27"/>
+    <x v="27"/>
+    <s v="Taco Bell"/>
+    <s v="Vadodara"/>
+    <s v="Blinkit"/>
+    <n v="470"/>
+  </r>
+  <r>
+    <x v="28"/>
+    <x v="28"/>
+    <s v="Hocco Eatery"/>
+    <s v="Ahmedabad"/>
+    <s v="Swiggy"/>
+    <n v="520"/>
+  </r>
+  <r>
+    <x v="29"/>
+    <x v="29"/>
+    <s v="Honest"/>
+    <s v="Surat"/>
+    <s v="Zomato"/>
+    <n v="350"/>
+  </r>
+  <r>
+    <x v="30"/>
+    <x v="30"/>
+    <s v="Domino's"/>
+    <s v="Vadodara"/>
+    <s v="Blinkit"/>
+    <n v="460"/>
+  </r>
+  <r>
+    <x v="31"/>
+    <x v="31"/>
+    <s v="McDonald's"/>
+    <s v="Ahmedabad"/>
+    <s v="Swiggy"/>
+    <n v="340"/>
+  </r>
+  <r>
+    <x v="32"/>
+    <x v="32"/>
+    <s v="KFC"/>
+    <s v="Rajkot"/>
+    <s v="Zomato"/>
+    <n v="620"/>
+  </r>
+  <r>
+    <x v="33"/>
+    <x v="33"/>
+    <s v="Pizza Hut"/>
+    <s v="Surat"/>
+    <s v="Blinkit"/>
+    <n v="780"/>
+  </r>
+  <r>
+    <x v="34"/>
+    <x v="34"/>
+    <s v="Subway"/>
+    <s v="Vadodara"/>
+    <s v="Swiggy"/>
+    <n v="300"/>
+  </r>
+  <r>
+    <x v="35"/>
+    <x v="35"/>
+    <s v="Burger King"/>
+    <s v="Ahmedabad"/>
+    <s v="Zomato"/>
+    <n v="430"/>
+  </r>
+  <r>
+    <x v="36"/>
+    <x v="36"/>
+    <s v="La Pino'z Pizza"/>
+    <s v="Surat"/>
+    <s v="Blinkit"/>
+    <n v="690"/>
+  </r>
+  <r>
+    <x v="37"/>
+    <x v="37"/>
+    <s v="Taco Bell"/>
+    <s v="Rajkot"/>
+    <s v="Swiggy"/>
+    <n v="490"/>
+  </r>
+  <r>
+    <x v="38"/>
+    <x v="38"/>
+    <s v="Hocco Eatery"/>
+    <s v="Vadodara"/>
+    <s v="Zomato"/>
+    <n v="550"/>
+  </r>
+  <r>
+    <x v="39"/>
+    <x v="39"/>
+    <s v="Honest"/>
+    <s v="Ahmedabad"/>
+    <s v="Blinkit"/>
+    <n v="370"/>
+  </r>
+  <r>
+    <x v="40"/>
+    <x v="40"/>
+    <s v="Domino's"/>
+    <s v="Surat"/>
+    <s v="Swiggy"/>
+    <n v="450"/>
+  </r>
+  <r>
+    <x v="41"/>
+    <x v="41"/>
+    <s v="McDonald's"/>
+    <s v="Rajkot"/>
+    <s v="Zomato"/>
+    <n v="340"/>
+  </r>
+  <r>
+    <x v="42"/>
+    <x v="42"/>
+    <s v="KFC"/>
+    <s v="Vadodara"/>
+    <s v="Blinkit"/>
+    <n v="600"/>
+  </r>
+  <r>
+    <x v="43"/>
+    <x v="43"/>
+    <s v="Pizza Hut"/>
+    <s v="Ahmedabad"/>
+    <s v="Swiggy"/>
+    <n v="740"/>
+  </r>
+  <r>
+    <x v="44"/>
+    <x v="44"/>
+    <s v="Subway"/>
+    <s v="Surat"/>
+    <s v="Zomato"/>
+    <n v="310"/>
+  </r>
+  <r>
+    <x v="45"/>
+    <x v="45"/>
+    <s v="Burger King"/>
+    <s v="Rajkot"/>
+    <s v="Blinkit"/>
+    <n v="440"/>
+  </r>
+  <r>
+    <x v="46"/>
+    <x v="46"/>
+    <s v="La Pino'z Pizza"/>
+    <s v="Vadodara"/>
+    <s v="Swiggy"/>
+    <n v="670"/>
+  </r>
+  <r>
+    <x v="47"/>
+    <x v="47"/>
+    <s v="Taco Bell"/>
+    <s v="Ahmedabad"/>
+    <s v="Zomato"/>
+    <n v="480"/>
+  </r>
+  <r>
+    <x v="48"/>
+    <x v="48"/>
+    <s v="Hocco Eatery"/>
+    <s v="Surat"/>
+    <s v="Blinkit"/>
+    <n v="560"/>
+  </r>
+  <r>
+    <x v="49"/>
+    <x v="49"/>
+    <s v="Honest"/>
+    <s v="Rajkot"/>
+    <s v="Swiggy"/>
+    <n v="360"/>
+  </r>
+  <r>
+    <x v="50"/>
+    <x v="50"/>
+    <s v="Domino's"/>
+    <s v="Ahmedabad"/>
+    <s v="Zomato"/>
+    <n v="470"/>
+  </r>
+  <r>
+    <x v="51"/>
+    <x v="51"/>
+    <s v="McDonald's"/>
+    <s v="Vadodara"/>
+    <s v="Blinkit"/>
+    <n v="350"/>
+  </r>
+  <r>
+    <x v="52"/>
+    <x v="52"/>
+    <s v="KFC"/>
+    <s v="Surat"/>
+    <s v="Swiggy"/>
+    <n v="630"/>
+  </r>
+  <r>
+    <x v="53"/>
+    <x v="53"/>
+    <s v="Pizza Hut"/>
+    <s v="Rajkot"/>
+    <s v="Zomato"/>
+    <n v="760"/>
+  </r>
+  <r>
+    <x v="54"/>
+    <x v="54"/>
+    <s v="Subway"/>
+    <s v="Ahmedabad"/>
+    <s v="Blinkit"/>
+    <n v="320"/>
+  </r>
+  <r>
+    <x v="55"/>
+    <x v="55"/>
+    <s v="Burger King"/>
+    <s v="Vadodara"/>
+    <s v="Swiggy"/>
+    <n v="450"/>
+  </r>
+  <r>
+    <x v="56"/>
+    <x v="56"/>
+    <s v="La Pino'z Pizza"/>
+    <s v="Surat"/>
+    <s v="Zomato"/>
+    <n v="710"/>
+  </r>
+  <r>
+    <x v="57"/>
+    <x v="57"/>
+    <s v="Taco Bell"/>
+    <s v="Rajkot"/>
+    <s v="Blinkit"/>
+    <n v="500"/>
+  </r>
+  <r>
+    <x v="58"/>
+    <x v="58"/>
+    <s v="Hocco Eatery"/>
+    <s v="Ahmedabad"/>
+    <s v="Swiggy"/>
+    <n v="580"/>
+  </r>
+  <r>
+    <x v="59"/>
+    <x v="59"/>
+    <s v="Honest"/>
+    <s v="Vadodara"/>
+    <s v="Zomato"/>
+    <n v="390"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6E20F71A-98C8-4F3F-B6DB-9D9D2A6A5EF8}" name="PivotTable6" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="I3:J64" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="6">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="121">
+        <item m="1" x="72"/>
+        <item m="1" x="78"/>
+        <item m="1" x="90"/>
+        <item m="1" x="60"/>
+        <item m="1" x="66"/>
+        <item m="1" x="84"/>
+        <item m="1" x="96"/>
+        <item m="1" x="102"/>
+        <item m="1" x="108"/>
+        <item m="1" x="114"/>
+        <item m="1" x="118"/>
+        <item m="1" x="61"/>
+        <item m="1" x="67"/>
+        <item m="1" x="73"/>
+        <item m="1" x="91"/>
+        <item m="1" x="79"/>
+        <item m="1" x="85"/>
+        <item m="1" x="97"/>
+        <item m="1" x="103"/>
+        <item m="1" x="109"/>
+        <item m="1" x="62"/>
+        <item m="1" x="115"/>
+        <item m="1" x="68"/>
+        <item m="1" x="92"/>
+        <item m="1" x="74"/>
+        <item m="1" x="80"/>
+        <item m="1" x="86"/>
+        <item m="1" x="98"/>
+        <item m="1" x="104"/>
+        <item m="1" x="110"/>
+        <item m="1" x="63"/>
+        <item m="1" x="116"/>
+        <item m="1" x="119"/>
+        <item m="1" x="81"/>
+        <item m="1" x="93"/>
+        <item m="1" x="69"/>
+        <item m="1" x="87"/>
+        <item m="1" x="99"/>
+        <item m="1" x="105"/>
+        <item m="1" x="111"/>
+        <item m="1" x="75"/>
+        <item m="1" x="82"/>
+        <item m="1" x="94"/>
+        <item m="1" x="117"/>
+        <item m="1" x="64"/>
+        <item m="1" x="70"/>
+        <item m="1" x="88"/>
+        <item m="1" x="100"/>
+        <item m="1" x="106"/>
+        <item m="1" x="112"/>
+        <item m="1" x="71"/>
+        <item m="1" x="76"/>
+        <item m="1" x="83"/>
+        <item m="1" x="95"/>
+        <item m="1" x="65"/>
+        <item m="1" x="89"/>
+        <item m="1" x="101"/>
+        <item m="1" x="107"/>
+        <item m="1" x="113"/>
+        <item m="1" x="77"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="61">
+    <i>
+      <x v="60"/>
+    </i>
+    <i>
+      <x v="61"/>
+    </i>
+    <i>
+      <x v="62"/>
+    </i>
+    <i>
+      <x v="63"/>
+    </i>
+    <i>
+      <x v="64"/>
+    </i>
+    <i>
+      <x v="65"/>
+    </i>
+    <i>
+      <x v="66"/>
+    </i>
+    <i>
+      <x v="67"/>
+    </i>
+    <i>
+      <x v="68"/>
+    </i>
+    <i>
+      <x v="69"/>
+    </i>
+    <i>
+      <x v="70"/>
+    </i>
+    <i>
+      <x v="71"/>
+    </i>
+    <i>
+      <x v="72"/>
+    </i>
+    <i>
+      <x v="73"/>
+    </i>
+    <i>
+      <x v="74"/>
+    </i>
+    <i>
+      <x v="75"/>
+    </i>
+    <i>
+      <x v="76"/>
+    </i>
+    <i>
+      <x v="77"/>
+    </i>
+    <i>
+      <x v="78"/>
+    </i>
+    <i>
+      <x v="79"/>
+    </i>
+    <i>
+      <x v="80"/>
+    </i>
+    <i>
+      <x v="81"/>
+    </i>
+    <i>
+      <x v="82"/>
+    </i>
+    <i>
+      <x v="83"/>
+    </i>
+    <i>
+      <x v="84"/>
+    </i>
+    <i>
+      <x v="85"/>
+    </i>
+    <i>
+      <x v="86"/>
+    </i>
+    <i>
+      <x v="87"/>
+    </i>
+    <i>
+      <x v="88"/>
+    </i>
+    <i>
+      <x v="89"/>
+    </i>
+    <i>
+      <x v="90"/>
+    </i>
+    <i>
+      <x v="91"/>
+    </i>
+    <i>
+      <x v="92"/>
+    </i>
+    <i>
+      <x v="93"/>
+    </i>
+    <i>
+      <x v="94"/>
+    </i>
+    <i>
+      <x v="95"/>
+    </i>
+    <i>
+      <x v="96"/>
+    </i>
+    <i>
+      <x v="97"/>
+    </i>
+    <i>
+      <x v="98"/>
+    </i>
+    <i>
+      <x v="99"/>
+    </i>
+    <i>
+      <x v="100"/>
+    </i>
+    <i>
+      <x v="101"/>
+    </i>
+    <i>
+      <x v="102"/>
+    </i>
+    <i>
+      <x v="103"/>
+    </i>
+    <i>
+      <x v="104"/>
+    </i>
+    <i>
+      <x v="105"/>
+    </i>
+    <i>
+      <x v="106"/>
+    </i>
+    <i>
+      <x v="107"/>
+    </i>
+    <i>
+      <x v="108"/>
+    </i>
+    <i>
+      <x v="109"/>
+    </i>
+    <i>
+      <x v="110"/>
+    </i>
+    <i>
+      <x v="111"/>
+    </i>
+    <i>
+      <x v="112"/>
+    </i>
+    <i>
+      <x v="113"/>
+    </i>
+    <i>
+      <x v="114"/>
+    </i>
+    <i>
+      <x v="115"/>
+    </i>
+    <i>
+      <x v="116"/>
+    </i>
+    <i>
+      <x v="117"/>
+    </i>
+    <i>
+      <x v="118"/>
+    </i>
+    <i>
+      <x v="119"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="13">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{87B270F2-118F-45D5-9CB5-A4957864FB2B}" name="PivotTable7" cacheId="37" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="I5:J18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0">
+      <items count="61">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" numFmtId="165" showAll="0">
+      <items count="61">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="369">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item sd="0" x="62"/>
+        <item sd="0" x="63"/>
+        <item sd="0" x="64"/>
+        <item sd="0" x="65"/>
+        <item sd="0" x="66"/>
+        <item sd="0" x="67"/>
+        <item sd="0" x="68"/>
+        <item sd="0" x="69"/>
+        <item sd="0" x="70"/>
+        <item sd="0" x="71"/>
+        <item sd="0" x="72"/>
+        <item sd="0" x="73"/>
+        <item sd="0" x="74"/>
+        <item sd="0" x="75"/>
+        <item sd="0" x="76"/>
+        <item sd="0" x="77"/>
+        <item sd="0" x="78"/>
+        <item sd="0" x="79"/>
+        <item sd="0" x="80"/>
+        <item sd="0" x="81"/>
+        <item sd="0" x="82"/>
+        <item sd="0" x="83"/>
+        <item sd="0" x="84"/>
+        <item sd="0" x="85"/>
+        <item sd="0" x="86"/>
+        <item sd="0" x="87"/>
+        <item sd="0" x="88"/>
+        <item sd="0" x="89"/>
+        <item sd="0" x="90"/>
+        <item sd="0" x="91"/>
+        <item sd="0" x="92"/>
+        <item sd="0" x="93"/>
+        <item sd="0" x="94"/>
+        <item sd="0" x="95"/>
+        <item sd="0" x="96"/>
+        <item sd="0" x="97"/>
+        <item sd="0" x="98"/>
+        <item sd="0" x="99"/>
+        <item sd="0" x="100"/>
+        <item sd="0" x="101"/>
+        <item sd="0" x="102"/>
+        <item sd="0" x="103"/>
+        <item sd="0" x="104"/>
+        <item sd="0" x="105"/>
+        <item sd="0" x="106"/>
+        <item sd="0" x="107"/>
+        <item sd="0" x="108"/>
+        <item sd="0" x="109"/>
+        <item sd="0" x="110"/>
+        <item sd="0" x="111"/>
+        <item sd="0" x="112"/>
+        <item sd="0" x="113"/>
+        <item sd="0" x="114"/>
+        <item sd="0" x="115"/>
+        <item sd="0" x="116"/>
+        <item sd="0" x="117"/>
+        <item sd="0" x="118"/>
+        <item sd="0" x="119"/>
+        <item sd="0" x="120"/>
+        <item sd="0" x="121"/>
+        <item sd="0" x="122"/>
+        <item sd="0" x="123"/>
+        <item sd="0" x="124"/>
+        <item sd="0" x="125"/>
+        <item sd="0" x="126"/>
+        <item sd="0" x="127"/>
+        <item sd="0" x="128"/>
+        <item sd="0" x="129"/>
+        <item sd="0" x="130"/>
+        <item sd="0" x="131"/>
+        <item sd="0" x="132"/>
+        <item sd="0" x="133"/>
+        <item sd="0" x="134"/>
+        <item sd="0" x="135"/>
+        <item sd="0" x="136"/>
+        <item sd="0" x="137"/>
+        <item sd="0" x="138"/>
+        <item sd="0" x="139"/>
+        <item sd="0" x="140"/>
+        <item sd="0" x="141"/>
+        <item sd="0" x="142"/>
+        <item sd="0" x="143"/>
+        <item sd="0" x="144"/>
+        <item sd="0" x="145"/>
+        <item sd="0" x="146"/>
+        <item sd="0" x="147"/>
+        <item sd="0" x="148"/>
+        <item sd="0" x="149"/>
+        <item sd="0" x="150"/>
+        <item sd="0" x="151"/>
+        <item sd="0" x="152"/>
+        <item sd="0" x="153"/>
+        <item sd="0" x="154"/>
+        <item sd="0" x="155"/>
+        <item sd="0" x="156"/>
+        <item sd="0" x="157"/>
+        <item sd="0" x="158"/>
+        <item sd="0" x="159"/>
+        <item sd="0" x="160"/>
+        <item sd="0" x="161"/>
+        <item sd="0" x="162"/>
+        <item sd="0" x="163"/>
+        <item sd="0" x="164"/>
+        <item sd="0" x="165"/>
+        <item sd="0" x="166"/>
+        <item sd="0" x="167"/>
+        <item sd="0" x="168"/>
+        <item sd="0" x="169"/>
+        <item sd="0" x="170"/>
+        <item sd="0" x="171"/>
+        <item sd="0" x="172"/>
+        <item sd="0" x="173"/>
+        <item sd="0" x="174"/>
+        <item sd="0" x="175"/>
+        <item sd="0" x="176"/>
+        <item sd="0" x="177"/>
+        <item sd="0" x="178"/>
+        <item sd="0" x="179"/>
+        <item sd="0" x="180"/>
+        <item sd="0" x="181"/>
+        <item sd="0" x="182"/>
+        <item sd="0" x="183"/>
+        <item sd="0" x="184"/>
+        <item sd="0" x="185"/>
+        <item sd="0" x="186"/>
+        <item sd="0" x="187"/>
+        <item sd="0" x="188"/>
+        <item sd="0" x="189"/>
+        <item sd="0" x="190"/>
+        <item sd="0" x="191"/>
+        <item sd="0" x="192"/>
+        <item sd="0" x="193"/>
+        <item sd="0" x="194"/>
+        <item sd="0" x="195"/>
+        <item sd="0" x="196"/>
+        <item sd="0" x="197"/>
+        <item sd="0" x="198"/>
+        <item sd="0" x="199"/>
+        <item sd="0" x="200"/>
+        <item sd="0" x="201"/>
+        <item sd="0" x="202"/>
+        <item sd="0" x="203"/>
+        <item sd="0" x="204"/>
+        <item sd="0" x="205"/>
+        <item sd="0" x="206"/>
+        <item sd="0" x="207"/>
+        <item sd="0" x="208"/>
+        <item sd="0" x="209"/>
+        <item sd="0" x="210"/>
+        <item sd="0" x="211"/>
+        <item sd="0" x="212"/>
+        <item sd="0" x="213"/>
+        <item sd="0" x="214"/>
+        <item sd="0" x="215"/>
+        <item sd="0" x="216"/>
+        <item sd="0" x="217"/>
+        <item sd="0" x="218"/>
+        <item sd="0" x="219"/>
+        <item sd="0" x="220"/>
+        <item sd="0" x="221"/>
+        <item sd="0" x="222"/>
+        <item sd="0" x="223"/>
+        <item sd="0" x="224"/>
+        <item sd="0" x="225"/>
+        <item sd="0" x="226"/>
+        <item sd="0" x="227"/>
+        <item sd="0" x="228"/>
+        <item sd="0" x="229"/>
+        <item sd="0" x="230"/>
+        <item sd="0" x="231"/>
+        <item sd="0" x="232"/>
+        <item sd="0" x="233"/>
+        <item sd="0" x="234"/>
+        <item sd="0" x="235"/>
+        <item sd="0" x="236"/>
+        <item sd="0" x="237"/>
+        <item sd="0" x="238"/>
+        <item sd="0" x="239"/>
+        <item sd="0" x="240"/>
+        <item sd="0" x="241"/>
+        <item sd="0" x="242"/>
+        <item sd="0" x="243"/>
+        <item sd="0" x="244"/>
+        <item sd="0" x="245"/>
+        <item sd="0" x="246"/>
+        <item sd="0" x="247"/>
+        <item sd="0" x="248"/>
+        <item sd="0" x="249"/>
+        <item sd="0" x="250"/>
+        <item sd="0" x="251"/>
+        <item sd="0" x="252"/>
+        <item sd="0" x="253"/>
+        <item sd="0" x="254"/>
+        <item sd="0" x="255"/>
+        <item sd="0" x="256"/>
+        <item sd="0" x="257"/>
+        <item sd="0" x="258"/>
+        <item sd="0" x="259"/>
+        <item sd="0" x="260"/>
+        <item sd="0" x="261"/>
+        <item sd="0" x="262"/>
+        <item sd="0" x="263"/>
+        <item sd="0" x="264"/>
+        <item sd="0" x="265"/>
+        <item sd="0" x="266"/>
+        <item sd="0" x="267"/>
+        <item sd="0" x="268"/>
+        <item sd="0" x="269"/>
+        <item sd="0" x="270"/>
+        <item sd="0" x="271"/>
+        <item sd="0" x="272"/>
+        <item sd="0" x="273"/>
+        <item sd="0" x="274"/>
+        <item sd="0" x="275"/>
+        <item sd="0" x="276"/>
+        <item sd="0" x="277"/>
+        <item sd="0" x="278"/>
+        <item sd="0" x="279"/>
+        <item sd="0" x="280"/>
+        <item sd="0" x="281"/>
+        <item sd="0" x="282"/>
+        <item sd="0" x="283"/>
+        <item sd="0" x="284"/>
+        <item sd="0" x="285"/>
+        <item sd="0" x="286"/>
+        <item sd="0" x="287"/>
+        <item sd="0" x="288"/>
+        <item sd="0" x="289"/>
+        <item sd="0" x="290"/>
+        <item sd="0" x="291"/>
+        <item sd="0" x="292"/>
+        <item sd="0" x="293"/>
+        <item sd="0" x="294"/>
+        <item sd="0" x="295"/>
+        <item sd="0" x="296"/>
+        <item sd="0" x="297"/>
+        <item sd="0" x="298"/>
+        <item sd="0" x="299"/>
+        <item sd="0" x="300"/>
+        <item sd="0" x="301"/>
+        <item sd="0" x="302"/>
+        <item sd="0" x="303"/>
+        <item sd="0" x="304"/>
+        <item sd="0" x="305"/>
+        <item sd="0" x="306"/>
+        <item sd="0" x="307"/>
+        <item sd="0" x="308"/>
+        <item sd="0" x="309"/>
+        <item sd="0" x="310"/>
+        <item sd="0" x="311"/>
+        <item sd="0" x="312"/>
+        <item sd="0" x="313"/>
+        <item sd="0" x="314"/>
+        <item sd="0" x="315"/>
+        <item sd="0" x="316"/>
+        <item sd="0" x="317"/>
+        <item sd="0" x="318"/>
+        <item sd="0" x="319"/>
+        <item sd="0" x="320"/>
+        <item sd="0" x="321"/>
+        <item sd="0" x="322"/>
+        <item sd="0" x="323"/>
+        <item sd="0" x="324"/>
+        <item sd="0" x="325"/>
+        <item sd="0" x="326"/>
+        <item sd="0" x="327"/>
+        <item sd="0" x="328"/>
+        <item sd="0" x="329"/>
+        <item sd="0" x="330"/>
+        <item sd="0" x="331"/>
+        <item sd="0" x="332"/>
+        <item sd="0" x="333"/>
+        <item sd="0" x="334"/>
+        <item sd="0" x="335"/>
+        <item sd="0" x="336"/>
+        <item sd="0" x="337"/>
+        <item sd="0" x="338"/>
+        <item sd="0" x="339"/>
+        <item sd="0" x="340"/>
+        <item sd="0" x="341"/>
+        <item sd="0" x="342"/>
+        <item sd="0" x="343"/>
+        <item sd="0" x="344"/>
+        <item sd="0" x="345"/>
+        <item sd="0" x="346"/>
+        <item sd="0" x="347"/>
+        <item sd="0" x="348"/>
+        <item sd="0" x="349"/>
+        <item sd="0" x="350"/>
+        <item sd="0" x="351"/>
+        <item sd="0" x="352"/>
+        <item sd="0" x="353"/>
+        <item sd="0" x="354"/>
+        <item sd="0" x="355"/>
+        <item sd="0" x="356"/>
+        <item sd="0" x="357"/>
+        <item sd="0" x="358"/>
+        <item sd="0" x="359"/>
+        <item sd="0" x="360"/>
+        <item sd="0" x="361"/>
+        <item sd="0" x="362"/>
+        <item sd="0" x="363"/>
+        <item sd="0" x="364"/>
+        <item sd="0" x="365"/>
+        <item sd="0" x="366"/>
+        <item sd="0" x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="3">
+    <field x="7"/>
+    <field x="6"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +3326,2933 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J64"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="10.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4">
+        <v>45778</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4">
+        <v>45870</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3">
+        <v>320</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="4">
+        <v>45992</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4">
+        <v>550</v>
+      </c>
+      <c r="I4" s="6">
+        <v>45778</v>
+      </c>
+      <c r="J4" s="3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4">
+        <v>45675</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>700</v>
+      </c>
+      <c r="I5" s="6">
+        <v>45870</v>
+      </c>
+      <c r="J5" s="3">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="4">
+        <v>45682</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6">
+        <v>280</v>
+      </c>
+      <c r="I6" s="6">
+        <v>45992</v>
+      </c>
+      <c r="J6" s="3">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="4">
+        <v>45687</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7">
+        <v>390</v>
+      </c>
+      <c r="I7" s="6">
+        <v>45675</v>
+      </c>
+      <c r="J7" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="4">
+        <v>45779</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8">
+        <v>620</v>
+      </c>
+      <c r="I8" s="6">
+        <v>45682</v>
+      </c>
+      <c r="J8" s="3">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="4">
+        <v>45902</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9">
+        <v>480</v>
+      </c>
+      <c r="I9" s="6">
+        <v>45687</v>
+      </c>
+      <c r="J9" s="3">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="4">
+        <v>45702</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10">
+        <v>540</v>
+      </c>
+      <c r="I10" s="6">
+        <v>45779</v>
+      </c>
+      <c r="J10" s="3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="4">
+        <v>45708</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11">
+        <v>360</v>
+      </c>
+      <c r="I11" s="6">
+        <v>45902</v>
+      </c>
+      <c r="J11" s="3">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="4">
+        <v>45713</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12">
+        <v>430</v>
+      </c>
+      <c r="I12" s="6">
+        <v>45702</v>
+      </c>
+      <c r="J12" s="3">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="4">
+        <v>45716</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13">
+        <v>510</v>
+      </c>
+      <c r="I13" s="6">
+        <v>45708</v>
+      </c>
+      <c r="J13" s="3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="4">
+        <v>45750</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14">
+        <v>610</v>
+      </c>
+      <c r="I14" s="6">
+        <v>45713</v>
+      </c>
+      <c r="J14" s="3">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="4">
+        <v>45903</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15">
+        <v>750</v>
+      </c>
+      <c r="I15" s="6">
+        <v>45716</v>
+      </c>
+      <c r="J15" s="3">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="4">
+        <v>45731</v>
+      </c>
+      <c r="C16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16">
+        <v>290</v>
+      </c>
+      <c r="I16" s="6">
+        <v>45750</v>
+      </c>
+      <c r="J16" s="3">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="4">
+        <v>45738</v>
+      </c>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17">
+        <v>420</v>
+      </c>
+      <c r="I17" s="6">
+        <v>45903</v>
+      </c>
+      <c r="J17" s="3">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="4">
+        <v>45744</v>
+      </c>
+      <c r="C18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18">
+        <v>680</v>
+      </c>
+      <c r="I18" s="6">
+        <v>45731</v>
+      </c>
+      <c r="J18" s="3">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="4">
+        <v>45747</v>
+      </c>
+      <c r="C19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19">
+        <v>460</v>
+      </c>
+      <c r="I19" s="6">
+        <v>45738</v>
+      </c>
+      <c r="J19" s="3">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="4">
+        <v>45751</v>
+      </c>
+      <c r="C20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20">
+        <v>530</v>
+      </c>
+      <c r="I20" s="6">
+        <v>45744</v>
+      </c>
+      <c r="J20" s="3">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="4">
+        <v>45934</v>
+      </c>
+      <c r="C21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21">
+        <v>340</v>
+      </c>
+      <c r="I21" s="6">
+        <v>45747</v>
+      </c>
+      <c r="J21" s="3">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="4">
+        <v>45762</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22">
+        <v>440</v>
+      </c>
+      <c r="I22" s="6">
+        <v>45751</v>
+      </c>
+      <c r="J22" s="3">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="4">
+        <v>45766</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23">
+        <v>330</v>
+      </c>
+      <c r="I23" s="6">
+        <v>45934</v>
+      </c>
+      <c r="J23" s="3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="4">
+        <v>45771</v>
+      </c>
+      <c r="C24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24">
+        <v>590</v>
+      </c>
+      <c r="I24" s="6">
+        <v>45762</v>
+      </c>
+      <c r="J24" s="3">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="4">
+        <v>45776</v>
+      </c>
+      <c r="C25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25">
+        <v>720</v>
+      </c>
+      <c r="I25" s="6">
+        <v>45766</v>
+      </c>
+      <c r="J25" s="3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="4">
+        <v>45782</v>
+      </c>
+      <c r="C26" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26">
+        <v>270</v>
+      </c>
+      <c r="I26" s="6">
+        <v>45771</v>
+      </c>
+      <c r="J26" s="3">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="4">
+        <v>45935</v>
+      </c>
+      <c r="C27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27">
+        <v>410</v>
+      </c>
+      <c r="I27" s="6">
+        <v>45776</v>
+      </c>
+      <c r="J27" s="3">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="4">
+        <v>45792</v>
+      </c>
+      <c r="C28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28">
+        <v>650</v>
+      </c>
+      <c r="I28" s="6">
+        <v>45782</v>
+      </c>
+      <c r="J28" s="3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="4">
+        <v>45797</v>
+      </c>
+      <c r="C29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29">
+        <v>470</v>
+      </c>
+      <c r="I29" s="6">
+        <v>45935</v>
+      </c>
+      <c r="J29" s="3">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="4">
+        <v>45802</v>
+      </c>
+      <c r="C30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30">
+        <v>520</v>
+      </c>
+      <c r="I30" s="6">
+        <v>45792</v>
+      </c>
+      <c r="J30" s="3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="4">
+        <v>45807</v>
+      </c>
+      <c r="C31" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31">
+        <v>350</v>
+      </c>
+      <c r="I31" s="6">
+        <v>45797</v>
+      </c>
+      <c r="J31" s="3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="4">
+        <v>45753</v>
+      </c>
+      <c r="C32" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32">
+        <v>460</v>
+      </c>
+      <c r="I32" s="6">
+        <v>45802</v>
+      </c>
+      <c r="J32" s="3">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="4">
+        <v>45906</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33">
+        <v>340</v>
+      </c>
+      <c r="I33" s="6">
+        <v>45807</v>
+      </c>
+      <c r="J33" s="3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="4">
+        <v>45822</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34">
+        <v>620</v>
+      </c>
+      <c r="I34" s="6">
+        <v>45753</v>
+      </c>
+      <c r="J34" s="3">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" s="4">
+        <v>45827</v>
+      </c>
+      <c r="C35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35">
+        <v>780</v>
+      </c>
+      <c r="I35" s="6">
+        <v>45906</v>
+      </c>
+      <c r="J35" s="3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="4">
+        <v>45832</v>
+      </c>
+      <c r="C36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36">
+        <v>300</v>
+      </c>
+      <c r="I36" s="6">
+        <v>45822</v>
+      </c>
+      <c r="J36" s="3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="4">
+        <v>45837</v>
+      </c>
+      <c r="C37" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37">
+        <v>430</v>
+      </c>
+      <c r="I37" s="6">
+        <v>45827</v>
+      </c>
+      <c r="J37" s="3">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38" s="4">
+        <v>45784</v>
+      </c>
+      <c r="C38" t="s">
+        <v>26</v>
+      </c>
+      <c r="D38" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38">
+        <v>690</v>
+      </c>
+      <c r="I38" s="6">
+        <v>45832</v>
+      </c>
+      <c r="J38" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="4">
+        <v>45937</v>
+      </c>
+      <c r="C39" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39">
+        <v>490</v>
+      </c>
+      <c r="I39" s="6">
+        <v>45837</v>
+      </c>
+      <c r="J39" s="3">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" s="4">
+        <v>45853</v>
+      </c>
+      <c r="C40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40">
+        <v>550</v>
+      </c>
+      <c r="I40" s="6">
+        <v>45784</v>
+      </c>
+      <c r="J40" s="3">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>62</v>
+      </c>
+      <c r="B41" s="4">
+        <v>45858</v>
+      </c>
+      <c r="C41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D41" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" t="s">
+        <v>17</v>
+      </c>
+      <c r="F41">
+        <v>370</v>
+      </c>
+      <c r="I41" s="6">
+        <v>45937</v>
+      </c>
+      <c r="J41" s="3">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42" s="4">
+        <v>45863</v>
+      </c>
+      <c r="C42" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42">
+        <v>450</v>
+      </c>
+      <c r="I42" s="6">
+        <v>45853</v>
+      </c>
+      <c r="J42" s="3">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>64</v>
+      </c>
+      <c r="B43" s="4">
+        <v>45868</v>
+      </c>
+      <c r="C43" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43">
+        <v>340</v>
+      </c>
+      <c r="I43" s="6">
+        <v>45858</v>
+      </c>
+      <c r="J43" s="3">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>65</v>
+      </c>
+      <c r="B44" s="4">
+        <v>45785</v>
+      </c>
+      <c r="C44" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" t="s">
+        <v>17</v>
+      </c>
+      <c r="F44">
+        <v>600</v>
+      </c>
+      <c r="I44" s="6">
+        <v>45863</v>
+      </c>
+      <c r="J44" s="3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>66</v>
+      </c>
+      <c r="B45" s="4">
+        <v>45938</v>
+      </c>
+      <c r="C45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45">
+        <v>740</v>
+      </c>
+      <c r="I45" s="6">
+        <v>45868</v>
+      </c>
+      <c r="J45" s="3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>67</v>
+      </c>
+      <c r="B46" s="4">
+        <v>45884</v>
+      </c>
+      <c r="C46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46">
+        <v>310</v>
+      </c>
+      <c r="I46" s="6">
+        <v>45785</v>
+      </c>
+      <c r="J46" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>68</v>
+      </c>
+      <c r="B47" s="4">
+        <v>45889</v>
+      </c>
+      <c r="C47" t="s">
+        <v>24</v>
+      </c>
+      <c r="D47" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47">
+        <v>440</v>
+      </c>
+      <c r="I47" s="6">
+        <v>45938</v>
+      </c>
+      <c r="J47" s="3">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>69</v>
+      </c>
+      <c r="B48" s="4">
+        <v>45894</v>
+      </c>
+      <c r="C48" t="s">
+        <v>26</v>
+      </c>
+      <c r="D48" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48">
+        <v>670</v>
+      </c>
+      <c r="I48" s="6">
+        <v>45884</v>
+      </c>
+      <c r="J48" s="3">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>70</v>
+      </c>
+      <c r="B49" s="4">
+        <v>45899</v>
+      </c>
+      <c r="C49" t="s">
+        <v>28</v>
+      </c>
+      <c r="D49" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" t="s">
+        <v>9</v>
+      </c>
+      <c r="F49">
+        <v>480</v>
+      </c>
+      <c r="I49" s="6">
+        <v>45889</v>
+      </c>
+      <c r="J49" s="3">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>71</v>
+      </c>
+      <c r="B50" s="4">
+        <v>45786</v>
+      </c>
+      <c r="C50" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50">
+        <v>560</v>
+      </c>
+      <c r="I50" s="6">
+        <v>45894</v>
+      </c>
+      <c r="J50" s="3">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>72</v>
+      </c>
+      <c r="B51" s="4">
+        <v>45939</v>
+      </c>
+      <c r="C51" t="s">
+        <v>32</v>
+      </c>
+      <c r="D51" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51">
+        <v>360</v>
+      </c>
+      <c r="I51" s="6">
+        <v>45899</v>
+      </c>
+      <c r="J51" s="3">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>73</v>
+      </c>
+      <c r="B52" s="4">
+        <v>45945</v>
+      </c>
+      <c r="C52" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" t="s">
+        <v>9</v>
+      </c>
+      <c r="F52">
+        <v>470</v>
+      </c>
+      <c r="I52" s="6">
+        <v>45786</v>
+      </c>
+      <c r="J52" s="3">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>74</v>
+      </c>
+      <c r="B53" s="4">
+        <v>45950</v>
+      </c>
+      <c r="C53" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53">
+        <v>350</v>
+      </c>
+      <c r="I53" s="6">
+        <v>45939</v>
+      </c>
+      <c r="J53" s="3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>75</v>
+      </c>
+      <c r="B54" s="4">
+        <v>45955</v>
+      </c>
+      <c r="C54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54">
+        <v>630</v>
+      </c>
+      <c r="I54" s="6">
+        <v>45945</v>
+      </c>
+      <c r="J54" s="3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>76</v>
+      </c>
+      <c r="B55" s="4">
+        <v>45960</v>
+      </c>
+      <c r="C55" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55" t="s">
+        <v>20</v>
+      </c>
+      <c r="E55" t="s">
+        <v>9</v>
+      </c>
+      <c r="F55">
+        <v>760</v>
+      </c>
+      <c r="I55" s="6">
+        <v>45950</v>
+      </c>
+      <c r="J55" s="3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>77</v>
+      </c>
+      <c r="B56" s="4">
+        <v>45788</v>
+      </c>
+      <c r="C56" t="s">
+        <v>22</v>
+      </c>
+      <c r="D56" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" t="s">
+        <v>17</v>
+      </c>
+      <c r="F56">
+        <v>320</v>
+      </c>
+      <c r="I56" s="6">
+        <v>45955</v>
+      </c>
+      <c r="J56" s="3">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>78</v>
+      </c>
+      <c r="B57" s="4">
+        <v>46002</v>
+      </c>
+      <c r="C57" t="s">
+        <v>24</v>
+      </c>
+      <c r="D57" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57">
+        <v>450</v>
+      </c>
+      <c r="I57" s="6">
+        <v>45960</v>
+      </c>
+      <c r="J57" s="3">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>79</v>
+      </c>
+      <c r="B58" s="4">
+        <v>45979</v>
+      </c>
+      <c r="C58" t="s">
+        <v>26</v>
+      </c>
+      <c r="D58" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" t="s">
+        <v>9</v>
+      </c>
+      <c r="F58">
+        <v>710</v>
+      </c>
+      <c r="I58" s="6">
+        <v>45788</v>
+      </c>
+      <c r="J58" s="3">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>80</v>
+      </c>
+      <c r="B59" s="4">
+        <v>45985</v>
+      </c>
+      <c r="C59" t="s">
+        <v>28</v>
+      </c>
+      <c r="D59" t="s">
+        <v>20</v>
+      </c>
+      <c r="E59" t="s">
+        <v>17</v>
+      </c>
+      <c r="F59">
+        <v>500</v>
+      </c>
+      <c r="I59" s="6">
+        <v>46002</v>
+      </c>
+      <c r="J59" s="3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>81</v>
+      </c>
+      <c r="B60" s="4">
+        <v>45789</v>
+      </c>
+      <c r="C60" t="s">
+        <v>30</v>
+      </c>
+      <c r="D60" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60">
+        <v>580</v>
+      </c>
+      <c r="I60" s="6">
+        <v>45979</v>
+      </c>
+      <c r="J60" s="3">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>82</v>
+      </c>
+      <c r="B61" s="4">
+        <v>46009</v>
+      </c>
+      <c r="C61" t="s">
+        <v>32</v>
+      </c>
+      <c r="D61" t="s">
+        <v>16</v>
+      </c>
+      <c r="E61" t="s">
+        <v>9</v>
+      </c>
+      <c r="F61">
+        <v>390</v>
+      </c>
+      <c r="I61" s="6">
+        <v>45985</v>
+      </c>
+      <c r="J61" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I62" s="6">
+        <v>45789</v>
+      </c>
+      <c r="J62" s="3">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I63" s="6">
+        <v>46009</v>
+      </c>
+      <c r="J63" s="3">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I64" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="J64" s="3">
+        <v>29600</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C09D1DA-6AFE-494B-88D7-FB7BD53F6FED}">
+  <dimension ref="A1:J61"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="7">
+        <v>45662</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="7">
+        <v>45665</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="7">
+        <v>45669</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="7">
+        <v>45675</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>700</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="7">
+        <v>45682</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6">
+        <v>280</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J6" s="3">
+        <v>2690</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="7">
+        <v>45687</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7">
+        <v>390</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J7" s="3">
+        <v>2940</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="7">
+        <v>45693</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8">
+        <v>620</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J8" s="3">
+        <v>3210</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="7">
+        <v>45697</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9">
+        <v>480</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J9" s="3">
+        <v>2950</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="7">
+        <v>45702</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10">
+        <v>540</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2670</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="7">
+        <v>45708</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11">
+        <v>360</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="J11" s="3">
+        <v>2930</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="7">
+        <v>45713</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12">
+        <v>430</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J12" s="3">
+        <v>2890</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="7">
+        <v>45716</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13">
+        <v>510</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J13" s="3">
+        <v>3240</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="7">
+        <v>45720</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14">
+        <v>610</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J14" s="3">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="7">
+        <v>45725</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15">
+        <v>750</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="J15" s="3">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="7">
+        <v>45731</v>
+      </c>
+      <c r="C16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16">
+        <v>290</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J16" s="3">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="7">
+        <v>45738</v>
+      </c>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17">
+        <v>420</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J17" s="3">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45744</v>
+      </c>
+      <c r="C18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18">
+        <v>680</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J18" s="3">
+        <v>29600</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45747</v>
+      </c>
+      <c r="C19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45751</v>
+      </c>
+      <c r="C20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45757</v>
+      </c>
+      <c r="C21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45762</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45766</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45771</v>
+      </c>
+      <c r="C24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45776</v>
+      </c>
+      <c r="C25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45782</v>
+      </c>
+      <c r="C26" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="7">
+        <v>45787</v>
+      </c>
+      <c r="C27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="7">
+        <v>45792</v>
+      </c>
+      <c r="C28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="7">
+        <v>45797</v>
+      </c>
+      <c r="C29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="7">
+        <v>45802</v>
+      </c>
+      <c r="C30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="7">
+        <v>45807</v>
+      </c>
+      <c r="C31" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="7">
+        <v>45812</v>
+      </c>
+      <c r="C32" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="7">
+        <v>45817</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="7">
+        <v>45822</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" s="7">
+        <v>45827</v>
+      </c>
+      <c r="C35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="7">
+        <v>45832</v>
+      </c>
+      <c r="C36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="7">
+        <v>45837</v>
+      </c>
+      <c r="C37" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38" s="7">
+        <v>45843</v>
+      </c>
+      <c r="C38" t="s">
+        <v>26</v>
+      </c>
+      <c r="D38" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="7">
+        <v>45848</v>
+      </c>
+      <c r="C39" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" s="7">
+        <v>45853</v>
+      </c>
+      <c r="C40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>62</v>
+      </c>
+      <c r="B41" s="7">
+        <v>45858</v>
+      </c>
+      <c r="C41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D41" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" t="s">
+        <v>17</v>
+      </c>
+      <c r="F41">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42" s="7">
+        <v>45863</v>
+      </c>
+      <c r="C42" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>64</v>
+      </c>
+      <c r="B43" s="7">
+        <v>45868</v>
+      </c>
+      <c r="C43" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>65</v>
+      </c>
+      <c r="B44" s="7">
+        <v>45874</v>
+      </c>
+      <c r="C44" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" t="s">
+        <v>17</v>
+      </c>
+      <c r="F44">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>66</v>
+      </c>
+      <c r="B45" s="7">
+        <v>45879</v>
+      </c>
+      <c r="C45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>67</v>
+      </c>
+      <c r="B46" s="7">
+        <v>45884</v>
+      </c>
+      <c r="C46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>68</v>
+      </c>
+      <c r="B47" s="7">
+        <v>45889</v>
+      </c>
+      <c r="C47" t="s">
+        <v>24</v>
+      </c>
+      <c r="D47" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>69</v>
+      </c>
+      <c r="B48" s="7">
+        <v>45894</v>
+      </c>
+      <c r="C48" t="s">
+        <v>26</v>
+      </c>
+      <c r="D48" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>70</v>
+      </c>
+      <c r="B49" s="7">
+        <v>45899</v>
+      </c>
+      <c r="C49" t="s">
+        <v>28</v>
+      </c>
+      <c r="D49" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" t="s">
+        <v>9</v>
+      </c>
+      <c r="F49">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>71</v>
+      </c>
+      <c r="B50" s="7">
+        <v>45905</v>
+      </c>
+      <c r="C50" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>72</v>
+      </c>
+      <c r="B51" s="7">
+        <v>45910</v>
+      </c>
+      <c r="C51" t="s">
+        <v>32</v>
+      </c>
+      <c r="D51" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>73</v>
+      </c>
+      <c r="B52" s="7">
+        <v>45945</v>
+      </c>
+      <c r="C52" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" t="s">
+        <v>9</v>
+      </c>
+      <c r="F52">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>74</v>
+      </c>
+      <c r="B53" s="7">
+        <v>45950</v>
+      </c>
+      <c r="C53" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>75</v>
+      </c>
+      <c r="B54" s="7">
+        <v>45955</v>
+      </c>
+      <c r="C54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>76</v>
+      </c>
+      <c r="B55" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C55" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55" t="s">
+        <v>20</v>
+      </c>
+      <c r="E55" t="s">
+        <v>9</v>
+      </c>
+      <c r="F55">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>77</v>
+      </c>
+      <c r="B56" s="7">
+        <v>45966</v>
+      </c>
+      <c r="C56" t="s">
+        <v>22</v>
+      </c>
+      <c r="D56" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" t="s">
+        <v>17</v>
+      </c>
+      <c r="F56">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>78</v>
+      </c>
+      <c r="B57" s="7">
+        <v>45973</v>
+      </c>
+      <c r="C57" t="s">
+        <v>24</v>
+      </c>
+      <c r="D57" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>79</v>
+      </c>
+      <c r="B58" s="7">
+        <v>45979</v>
+      </c>
+      <c r="C58" t="s">
+        <v>26</v>
+      </c>
+      <c r="D58" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" t="s">
+        <v>9</v>
+      </c>
+      <c r="F58">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>80</v>
+      </c>
+      <c r="B59" s="7">
+        <v>45985</v>
+      </c>
+      <c r="C59" t="s">
+        <v>28</v>
+      </c>
+      <c r="D59" t="s">
+        <v>20</v>
+      </c>
+      <c r="E59" t="s">
+        <v>17</v>
+      </c>
+      <c r="F59">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>81</v>
+      </c>
+      <c r="B60" s="7">
+        <v>45996</v>
+      </c>
+      <c r="C60" t="s">
+        <v>30</v>
+      </c>
+      <c r="D60" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>82</v>
+      </c>
+      <c r="B61" s="7">
+        <v>46009</v>
+      </c>
+      <c r="C61" t="s">
+        <v>32</v>
+      </c>
+      <c r="D61" t="s">
+        <v>16</v>
+      </c>
+      <c r="E61" t="s">
+        <v>9</v>
+      </c>
+      <c r="F61">
+        <v>390</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>